--- a/excel outputs/דוח נכסים לתאריך:22-07-2026.xlsx
+++ b/excel outputs/דוח נכסים לתאריך:22-07-2026.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="עסקים בירושלים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח עסקים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'דוח עסקים'!$A$1:$G$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,11 +31,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -51,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F8FF"/>
-        <bgColor rgb="00F0F8FF"/>
+        <fgColor rgb="00DEEAF1"/>
+        <bgColor rgb="00DEEAF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,13 +458,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -505,20 +507,20 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>בית הקרפיון</t>
+          <t>קידום ושילוב חינוכי בע"מ</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 18</t>
+          <t>בהרן שלמה זלמן 6, ירושלים</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>מכירת דגים</t>
+          <t>שירותי חינוך</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -526,32 +528,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/62221290/11660/</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.b144.co.il/b144_sip/4A1404134470655D491602114C73665B48/</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>"אייזנבך" סוכנות נסיעות</t>
+          <t>בן-שלום יעקב</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 19</t>
+          <t>בוסתנאי 30, ירושלים</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>סוכנות נסיעות</t>
+          <t>צביעה ושיפוצים</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -561,26 +555,26 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/2607370/34680/</t>
+          <t>https://www.d.co.il/6154270/41670/</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>מרכז השעונים והאלקטרוניקה</t>
+          <t>simpleline</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 19</t>
+          <t>בוסתנאי 32, ירושלים</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>שעונים ואלקטרוניקה</t>
+          <t>תכשיטים</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -590,26 +584,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/19935420/49560/</t>
+          <t>https://www.d.co.il/80310761/50850/</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>אדון ירושלים</t>
+          <t>נגיעה בעץ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 2</t>
+          <t>בורוכוב 22, ירושלים</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>אופנת גברים</t>
+          <t>פרגולות והצללה</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -619,26 +613,26 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/5705490/4280/</t>
+          <t>https://www.d.co.il/80163803/40480/</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>"קונטרס" - עיתון בצרפתית</t>
+          <t>אורלי בניית ציפורניים</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 2</t>
+          <t>בורוכוב 57, ירושלים</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>עיתון</t>
+          <t>בניית ציפורניים ומניקור</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -648,26 +642,26 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/15641110/38220/</t>
+          <t>https://www.d.co.il/80177060/42275/</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>טויסקידס</t>
+          <t>ד"ר פליישמן צבי</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 2</t>
+          <t>בורוכוב 60, ירושלים</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>צעצועים</t>
+          <t>רופא וטרינרי</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -677,26 +671,26 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/80265191/42900/</t>
+          <t>https://www.d.co.il/33125270/14670/</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>היד השניה</t>
+          <t>הירשביין אדגר</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 24</t>
+          <t>ביאליק 5, ירושלים</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>רהיטים יד שניה</t>
+          <t>צילום פרסום ואופנה</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -706,26 +700,26 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/80015958/46080/</t>
+          <t>https://www.d.co.il/5847480/42390/</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>צמצם שטטנר</t>
+          <t>גרשמן גילדה</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 3</t>
+          <t>ביאליק 5, ירושלים</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>אופטיקה וצילום</t>
+          <t>פסיכולוג קליני</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -735,26 +729,26 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/64629720/41790/</t>
+          <t>https://www.d.co.il/18257360/40270/</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>משכנצ'יק - משכנתא בראש שקט</t>
+          <t>א.פטרוב מדידות הנדסה בע"מ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 3</t>
+          <t>ביצור יהושע 3, ירושלים</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>משכנתאות</t>
+          <t>מדידות הנדסיות</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -764,26 +758,26 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/80109292/6650/</t>
+          <t>https://www.d.co.il/80263315/23790/</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>מאגר דירות</t>
+          <t>תמיר כהן</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 3</t>
+          <t>ביצור יהושע 3, ירושלים</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>תיווך נדל"ן</t>
+          <t>מהנדסי חשמל</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -793,26 +787,26 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/76970140/32970/</t>
+          <t>https://www.d.co.il/80205258/23762/</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>הלפרין הרב שמואל אלעזר</t>
+          <t>איריס סיוון</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 3</t>
+          <t>ביצור יהושע 5, ירושלים</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>שירותים מקצועיים</t>
+          <t>לימודי פיתוח קול</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -822,26 +816,26 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/15848870/45510/</t>
+          <t>https://www.d.co.il/80045982/39740/</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>תכשיטי הכיכר</t>
+          <t>עו"ד ונוטריון גורל אהרון</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 3</t>
+          <t>בושם 1, ירושלים</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>תכשיטים</t>
+          <t>עורכי דין ונוטריון</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -849,28 +843,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80213982/50850/</t>
-        </is>
-      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>קופי מא"ש</t>
+          <t>אור לילד</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 30</t>
+          <t>בושם 1, ירושלים</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>שירותי צילום ומסמכים</t>
+          <t>גני ילדים ומעונות יום</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -878,28 +868,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/76608890/14040/</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>לנדמן ישראל "תפארת"</t>
+          <t>אבנים מבורכות</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 39</t>
+          <t>בושם 1, ירושלים</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>כלי כסף</t>
+          <t>תכשיטים</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -907,28 +893,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5825280/21270/</t>
-        </is>
-      </c>
+      <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>אופני בר-עמי</t>
+          <t>בוטיק ירושלמי ללא גלוטן</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 4</t>
+          <t>בושם 2, ירושלים</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>אופניים</t>
+          <t>קורסי בישול ואפייה</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -936,28 +918,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/31313490/1950/</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>חסדי נעמי</t>
+          <t>עו"ד גבעתי יאיר</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 5</t>
+          <t>בורלא יהודה 27, ירושלים</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>שירותי חסד וגמ"ח</t>
+          <t>עורכי דין - דיני מקרקעין</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -965,28 +943,24 @@
           <t>גבוה</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/65768050/300/</t>
-        </is>
-      </c>
+      <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>מעבדת גאולה</t>
+          <t>חיים גיבתי ושות' משרד עורכי דין</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ב אונגר מאה שערים 5</t>
+          <t>בורלא יהודה 27, ירושלים</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>מעבדה</t>
+          <t>משרד עורכי דין</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -996,709 +970,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.d.co.il/80218901/41760/</t>
+          <t>https://www.givatilaw.co.il</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>מלאכת מחשבת</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 5</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>גלריה ואמנות</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/21681770/10160/</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ש.כהן ספרים בע"מ</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 6</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>ספרים</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/9034840/36570/</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>מעבדה לבירור שעטנז</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 6</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>מעבדה לשעטנז</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/2508030/30630/</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ויזל אייז'ק</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 6</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>שירותים</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/37881300/45870/</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>גל-אור בר עמי</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 6</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>חנות כללית</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/62160550/17850/</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>גל-אור</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 6</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>רהיטים</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/9035670/29740/</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>מגדנית בריזל</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 68</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>מגדניה ומאפה</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5797630/22620/</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>אופנת עדן</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>אופנה</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/35066490/16865/</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>כהן גרשון העניך - "המפיץ"</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 70</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>הפצה</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5825100/52170/</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>מפעלי הנצחה קרן קיימת כולל שומרי החומות</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 75</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>גמ"ח ושירותים</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5824030/270/</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>כולל שומרי החומות לצדקת רבי מאיר בעל הנס</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 75</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>גמ"ח וצדקה</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/475890/20010/</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>"היכל" תשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 72</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>תשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/21681850/52170/</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>ק.ס.ת קניגסברג</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 72</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>תשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/101650/52170/</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>מרקוביץ-רקמה תשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 8</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>רקמה ותשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80069310/52170/</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>כולל אמריקה תפארת ירושלים</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 8</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>גמ"חים ושירותים</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/1826830/10170/</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>רבינוביץ יעקב</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 8</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>תשמישי קדושה</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/10233400/52170/</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>יד שניה ורהיטים עתיקים</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 83</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>רהיטים עתיקים</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/38147460/46080/</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>דויטש</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 83</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>בית מרקחת</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5826760/8150/</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>מגדנית בריזל</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 9</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>מגדניה ומאפה</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5797710/8930/</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>אופנת הנסיכה</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 9</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>אופנה</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/38125000/16865/</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>הטאבון הירושלמי</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>באום שלמה 2</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>מסעדה</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80341937/30420/</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>איחוד הישיבות בא"י</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 71</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>ישיבות וכוללים</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/5789630/38220/</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>גוד מרקט</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 42</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>סופרמרקט</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>https://pricepilot.co.il/store/%D7%9E%D7%90%D7%94%20%D7%A9%D7%A2%D7%A8%D7%99%D7%9D%2042,%20%D7%99%D7%A8%D7%95%D7%A9%D7%9C%D7%99%D7%9D/6f2228b5-ca79-443f-9813-d89fd8c6dd54</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>קצביה - מאה שערים 31</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>ב אונגר מאה שערים 31</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>קצביה</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/h-c2490-e0-p0-l0-city3000/</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>